--- a/Tabelas/casos_por_regiao.xlsx
+++ b/Tabelas/casos_por_regiao.xlsx
@@ -450,7 +450,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1636</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="3">
@@ -463,7 +463,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1411</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="4">
@@ -476,7 +476,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>689</v>
+        <v>752</v>
       </c>
     </row>
     <row r="5">
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1471</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>598</v>
+        <v>621</v>
       </c>
     </row>
   </sheetData>
